--- a/04_input_files/wes_commercial_tally.xlsx
+++ b/04_input_files/wes_commercial_tally.xlsx
@@ -1,192 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mattg\Desktop\github\FWC-estimation-method\04_input_files\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4A7FF2-A92E-4FDD-B011-C67C7D8921D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="53">
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>season</t>
-  </si>
-  <si>
-    <t>private_tally</t>
-  </si>
-  <si>
-    <t>commercial_tally</t>
-  </si>
-  <si>
-    <t>charter_tally</t>
-  </si>
-  <si>
-    <t>2024-12-03</t>
-  </si>
-  <si>
-    <t>2024-25</t>
-  </si>
-  <si>
-    <t>2024-12-04</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>2024-12-06</t>
-  </si>
-  <si>
-    <t>2024-12-07</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>2024-12-12</t>
-  </si>
-  <si>
-    <t>2024-12-13</t>
-  </si>
-  <si>
-    <t>2024-12-14</t>
-  </si>
-  <si>
-    <t>2024-12-15</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>2024-12-20</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>2024-12-22</t>
-  </si>
-  <si>
-    <t>2024-12-23</t>
-  </si>
-  <si>
-    <t>2024-12-24</t>
-  </si>
-  <si>
-    <t>2024-12-26</t>
-  </si>
-  <si>
-    <t>2024-12-27</t>
-  </si>
-  <si>
-    <t>2024-12-28</t>
-  </si>
-  <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
-    <t>2025-01-02</t>
-  </si>
-  <si>
-    <t>2025-01-03</t>
-  </si>
-  <si>
-    <t>2025-01-04</t>
-  </si>
-  <si>
-    <t>2025-01-07</t>
-  </si>
-  <si>
-    <t>2025-01-08</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>2025-01-10</t>
-  </si>
-  <si>
-    <t>2025-01-11</t>
-  </si>
-  <si>
-    <t>2025-01-14</t>
-  </si>
-  <si>
-    <t>2025-01-16</t>
-  </si>
-  <si>
-    <t>2025-01-17</t>
-  </si>
-  <si>
-    <t>2025-01-18</t>
-  </si>
-  <si>
-    <t>2025-01-21</t>
-  </si>
-  <si>
-    <t>2025-01-22</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>2025-01-29</t>
-  </si>
-  <si>
-    <t>2025-01-30</t>
-  </si>
-  <si>
-    <t>2025-01-31</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>2025-02-06</t>
-  </si>
-  <si>
-    <t>2025-02-07</t>
-  </si>
-  <si>
-    <t>2025-02-08</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -214,22 +52,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -517,40 +350,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J71"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>private_tally</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>commercial_tally</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>charter_tally</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>private_interviewed</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>commercial_interviewed</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>charter_interviewed</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
       </c>
       <c r="C2">
         <v>5</v>
@@ -561,13 +426,31 @@
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
       </c>
       <c r="C3">
         <v>7</v>
@@ -578,13 +461,36 @@
       <c r="E3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>knotty girl went out but not for crab</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
       </c>
       <c r="C4">
         <v>3</v>
@@ -595,13 +501,36 @@
       <c r="E4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>missed 1 boat at BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
       </c>
       <c r="C5">
         <v>4</v>
@@ -612,13 +541,31 @@
       <c r="E5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
       </c>
       <c r="C6">
         <v>1</v>
@@ -629,13 +576,36 @@
       <c r="E6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>missed the ultimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
       </c>
       <c r="C7">
         <v>0</v>
@@ -646,13 +616,36 @@
       <c r="E7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>missed 1 comm, charter was not crabbing. Started tally</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
       </c>
       <c r="C8">
         <v>1</v>
@@ -663,13 +656,31 @@
       <c r="E8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
       </c>
       <c r="C9">
         <v>1</v>
@@ -680,13 +691,31 @@
       <c r="E9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
       </c>
       <c r="C10">
         <v>1</v>
@@ -697,13 +726,31 @@
       <c r="E10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
       </c>
       <c r="C11">
         <v>0</v>
@@ -714,13 +761,31 @@
       <c r="E11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
       </c>
       <c r="C12">
         <v>4</v>
@@ -731,13 +796,31 @@
       <c r="E12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
       </c>
       <c r="C13">
         <v>3</v>
@@ -748,13 +831,36 @@
       <c r="E13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>rec = 3 bl, cluster duck (marina). Missed 1 rec boat</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
       </c>
       <c r="C14">
         <v>1</v>
@@ -765,13 +871,36 @@
       <c r="E14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>missed 1 rec boat</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
       </c>
       <c r="C15">
         <v>2</v>
@@ -782,13 +911,31 @@
       <c r="E15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
       </c>
       <c r="C16">
         <v>2</v>
@@ -799,13 +946,31 @@
       <c r="E16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" t="s">
-        <v>21</v>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2024-12-23</t>
+        </is>
       </c>
       <c r="C17">
         <v>1</v>
@@ -816,13 +981,36 @@
       <c r="E17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
         <v>6</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>missed betty lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
       </c>
       <c r="C18">
         <v>2</v>
@@ -833,13 +1021,31 @@
       <c r="E18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
+        </is>
       </c>
       <c r="C19">
         <v>1</v>
@@ -850,13 +1056,31 @@
       <c r="E19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
       </c>
       <c r="C20">
         <v>3</v>
@@ -867,13 +1091,36 @@
       <c r="E20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>monte carlo - CG check</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-12-28</t>
+        </is>
       </c>
       <c r="C21">
         <v>8</v>
@@ -884,13 +1131,36 @@
       <c r="E21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" t="s">
-        <v>26</v>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>rec = 3 bl, 3 marina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
       </c>
       <c r="C22">
         <v>5</v>
@@ -901,13 +1171,36 @@
       <c r="E22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
         <v>6</v>
       </c>
-      <c r="B23" t="s">
-        <v>27</v>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>alma jayne test run, miss kathleen missed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
       </c>
       <c r="C23">
         <v>3</v>
@@ -918,13 +1211,36 @@
       <c r="E23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" t="s">
-        <v>28</v>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>no trailers lefts</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
       </c>
       <c r="C24">
         <v>3</v>
@@ -935,13 +1251,36 @@
       <c r="E24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" t="s">
-        <v>29</v>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>no trailers lefts</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-01-03</t>
+        </is>
       </c>
       <c r="C25">
         <v>1</v>
@@ -952,13 +1291,36 @@
       <c r="E25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" t="s">
-        <v>30</v>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1 rec still out</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
       </c>
       <c r="C26">
         <v>3</v>
@@ -969,13 +1331,31 @@
       <c r="E26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" t="s">
-        <v>31</v>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-01-07</t>
+        </is>
       </c>
       <c r="C27">
         <v>4</v>
@@ -986,13 +1366,31 @@
       <c r="E27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" t="s">
-        <v>32</v>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-01-08</t>
+        </is>
       </c>
       <c r="C28">
         <v>6</v>
@@ -1003,13 +1401,36 @@
       <c r="E28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" t="s">
-        <v>33</v>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>3 rec boats still out</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1020,13 +1441,36 @@
       <c r="E29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" t="s">
-        <v>34</v>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1 trailer left</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1037,13 +1481,31 @@
       <c r="E30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" t="s">
-        <v>35</v>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-01-11</t>
+        </is>
       </c>
       <c r="C31">
         <v>2</v>
@@ -1054,13 +1516,31 @@
       <c r="E31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" t="s">
-        <v>36</v>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
       </c>
       <c r="C32">
         <v>5</v>
@@ -1071,13 +1551,36 @@
       <c r="E32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" t="s">
-        <v>37</v>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32">
+        <v>4</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1 comm, 1 rec still out</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
       </c>
       <c r="C33">
         <v>0</v>
@@ -1088,13 +1591,31 @@
       <c r="E33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" t="s">
-        <v>38</v>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1105,13 +1626,31 @@
       <c r="E34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" t="s">
-        <v>39</v>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-01-18</t>
+        </is>
       </c>
       <c r="C35">
         <v>7</v>
@@ -1122,13 +1661,31 @@
       <c r="E35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" t="s">
-        <v>40</v>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
       </c>
       <c r="C36">
         <v>1</v>
@@ -1139,13 +1696,31 @@
       <c r="E36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
         <v>6</v>
       </c>
-      <c r="B37" t="s">
-        <v>41</v>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1156,13 +1731,31 @@
       <c r="E37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-01-23</t>
+        </is>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1173,13 +1766,31 @@
       <c r="E38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
         <v>6</v>
       </c>
-      <c r="B39" t="s">
-        <v>43</v>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-01-24</t>
+        </is>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1190,13 +1801,36 @@
       <c r="E39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" t="s">
-        <v>44</v>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>3</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>interivewed 3 out of 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
       </c>
       <c r="C40">
         <v>5</v>
@@ -1207,13 +1841,31 @@
       <c r="E40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" t="s">
-        <v>45</v>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
       </c>
       <c r="C41">
         <v>4</v>
@@ -1224,13 +1876,31 @@
       <c r="E41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" t="s">
-        <v>46</v>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1241,13 +1911,31 @@
       <c r="E42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43" t="s">
-        <v>47</v>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>7</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1258,13 +1946,31 @@
       <c r="E43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" t="s">
-        <v>48</v>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1275,13 +1981,31 @@
       <c r="E44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" t="s">
-        <v>49</v>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
       </c>
       <c r="C45">
         <v>0</v>
@@ -1292,13 +2016,31 @@
       <c r="E45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" t="s">
-        <v>50</v>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
       </c>
       <c r="C46">
         <v>0</v>
@@ -1309,42 +2051,927 @@
       <c r="E46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>4</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>tally sheet</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>missed 1 rec boat</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>8</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>7</v>
+      </c>
+      <c r="G49">
+        <v>3</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>7</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>7</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51">
         <v>6</v>
       </c>
-      <c r="B47" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>2</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>4</v>
+      </c>
+      <c r="G51">
+        <v>3</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="C52">
         <v>6</v>
       </c>
-      <c r="B48" t="s">
-        <v>52</v>
-      </c>
-      <c r="C48">
-        <v>2</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
+      <c r="D52">
+        <v>2</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>8</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>7</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>5</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <v>3</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>5</v>
+      </c>
+      <c r="D56">
+        <v>6</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>5</v>
+      </c>
+      <c r="G56">
+        <v>5</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>3</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>4</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>4</v>
+      </c>
+      <c r="G58">
+        <v>3</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>2</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61">
+        <v>5</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61">
+        <v>3</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>6</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>6</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63">
+        <v>8</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <v>8</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>5</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>2</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>2</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>7</v>
+      </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66">
+        <v>4</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>last day for S rec crab trips, S gear set 12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>3</v>
+      </c>
+      <c r="G67">
+        <v>3</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>hustler as commercial</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>S commercial opens</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>5</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>5</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>N gear set</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>6</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>6</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>2</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>N commercial opens 1/4</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>